--- a/Sematic_SoDoNguyenLy/Schematic_study.xlsx
+++ b/Sematic_SoDoNguyenLy/Schematic_study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Sematic_SoDoNguyenLy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211A1005-3D7B-44A6-B517-7D1D4232AB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290F6628-EA4D-43AC-BBB1-39C1FD0223CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D15D3355-C5E5-40D1-9E25-1D8BB52CA4EC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="213">
   <si>
     <t>🧩 I. CÁC PHẦN TỬ CƠ BẢN – LINH KIỆN PHỔ BIẾN</t>
   </si>
@@ -419,12 +419,600 @@
   <si>
     <t xml:space="preserve">	BLM21PG, MPZ1608, 600Ω @ 100MHz</t>
   </si>
+  <si>
+    <t>🔋 1. PMIC là gì?</t>
+  </si>
+  <si>
+    <r>
+      <t>PMIC (Power Management Integrated Circuit)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là IC quản lý nguồn, có nhiệm vụ:</t>
+    </r>
+  </si>
+  <si>
+    <t>Chuyển đổi điện áp (buck, boost, LDO...)</t>
+  </si>
+  <si>
+    <t>Bật/tắt các rail nguồn theo thứ tự đúng</t>
+  </si>
+  <si>
+    <t>Giám sát điện áp, dòng, nhiệt độ</t>
+  </si>
+  <si>
+    <t>Cung cấp nguồn cho SoC, RAM, các cảm biến, thiết bị ngoại vi, v.v.</t>
+  </si>
+  <si>
+    <t>🧠 2. Vai trò của PMIC trong BSP</t>
+  </si>
+  <si>
+    <t>Trong BSP, phần mềm cần tương tác với phần cứng, và PMIC là một phần thiết yếu của hệ thống cấp nguồn. Do đó, BSP phải hỗ trợ PMIC ở các cấp độ sau:</t>
+  </si>
+  <si>
+    <t>2.1. Device Tree (DT) / Board Configuration</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BSP chứa thông tin về </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cấu hình PMIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong Device Tree (Linux) hoặc các tập tin cấu hình tương tự.</t>
+    </r>
+  </si>
+  <si>
+    <t>Định nghĩa các rail nguồn, thứ tự bật nguồn, tương ứng với các thiết bị.</t>
+  </si>
+  <si>
+    <t>2.2. Driver</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BSP cần có </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>driver PMIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để:</t>
+    </r>
+  </si>
+  <si>
+    <t>Giao tiếp với PMIC qua I2C/SPI</t>
+  </si>
+  <si>
+    <t>Điều khiển điện áp từng rail</t>
+  </si>
+  <si>
+    <t>Quản lý bật/tắt từng nguồn</t>
+  </si>
+  <si>
+    <t>Hỗ trợ chế độ sleep / suspend / resume</t>
+  </si>
+  <si>
+    <t>2.3. Power Sequencing</t>
+  </si>
+  <si>
+    <t>PMIC hỗ trợ các chế độ bật nguồn tuần tự theo yêu cầu của SoC.</t>
+  </si>
+  <si>
+    <t>BSP đảm bảo thứ tự cấp nguồn đúng (VD: cấp nguồn VDD_CORE trước VDD_IO).</t>
+  </si>
+  <si>
+    <t>2.4. Thermal and Power Monitoring</t>
+  </si>
+  <si>
+    <t>Một số PMIC có chức năng giám sát nhiệt độ và báo quá nhiệt.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BSP có thể đăng ký </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thermal zone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sử dụng PMIC để theo dõi.</t>
+    </r>
+  </si>
+  <si>
+    <t>2.5. Power Modes / Suspend</t>
+  </si>
+  <si>
+    <t>PMIC hỗ trợ nhiều chế độ tiết kiệm điện (sleep, standby).</t>
+  </si>
+  <si>
+    <t>BSP điều khiển qua driver để vào/thoát chế độ này khi hệ thống cần giảm tiêu thụ điện.</t>
+  </si>
+  <si>
+    <t>Hãng</t>
+  </si>
+  <si>
+    <t>PMIC phổ biến</t>
+  </si>
+  <si>
+    <t>Tương thích với SoC</t>
+  </si>
+  <si>
+    <t>NXP</t>
+  </si>
+  <si>
+    <t>PF1550, PF8100</t>
+  </si>
+  <si>
+    <t>i.MX8, i.MX6</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>TPS65910, LP8731</t>
+  </si>
+  <si>
+    <t>AM335x, Sitara</t>
+  </si>
+  <si>
+    <t>ROHM</t>
+  </si>
+  <si>
+    <t>BD71847AMWV</t>
+  </si>
+  <si>
+    <t>i.MX8M</t>
+  </si>
+  <si>
+    <t>Dialog</t>
+  </si>
+  <si>
+    <t>DA9063</t>
+  </si>
+  <si>
+    <t>ARM/ARM64</t>
+  </si>
+  <si>
+    <t>Thành phần BSP</t>
+  </si>
+  <si>
+    <t>Vai trò với PMIC</t>
+  </si>
+  <si>
+    <t>Device Tree</t>
+  </si>
+  <si>
+    <t>Mô tả PMIC, map nguồn, thiết lập điện áp</t>
+  </si>
+  <si>
+    <t>Drivers</t>
+  </si>
+  <si>
+    <t>Giao tiếp và điều khiển PMIC</t>
+  </si>
+  <si>
+    <t>Regulator Framework (Linux)</t>
+  </si>
+  <si>
+    <t>API để kernel và user-space điều khiển nguồn</t>
+  </si>
+  <si>
+    <t>Power Management</t>
+  </si>
+  <si>
+    <t>Tích hợp suspend/resume, DVFS</t>
+  </si>
+  <si>
+    <t>Thermal subsystem</t>
+  </si>
+  <si>
+    <t>(nếu có) tích hợp thông tin nhiệt độ từ PMIC</t>
+  </si>
+  <si>
+    <t>PMIC (Power Management IC) chịu trách nhiệm quản lý và phân phối điện áp cho các khối chức năng khác nhau trên bo mạch. Dưới đây là cái nhìn tổng quan và chi tiết về PMIC cũng như mối liên hệ của nó với BSP:</t>
+  </si>
+  <si>
+    <t>🔌 Rail nguồn là gì?</t>
+  </si>
+  <si>
+    <t>Thành phần</t>
+  </si>
+  <si>
+    <t>Ý nghĩa</t>
+  </si>
+  <si>
+    <t>Điện áp</t>
+  </si>
+  <si>
+    <t>Mỗi rail cung cấp một mức điện áp cố định (VD: 1.8V, 3.3V, 5V)</t>
+  </si>
+  <si>
+    <t>Dòng điện</t>
+  </si>
+  <si>
+    <t>Mỗi rail được thiết kế để cấp dòng điện phù hợp cho nhóm thiết bị</t>
+  </si>
+  <si>
+    <t>Tên gọi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VDD_CORE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VDD_IO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VDD_DDR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VCC_3V3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>VDD_ANA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AVDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,...</t>
+    </r>
+  </si>
+  <si>
+    <t>🎯 Tại sao có nhiều rail nguồn?</t>
+  </si>
+  <si>
+    <t>Vì các thành phần khác nhau trên bo mạch có yêu cầu điện áp khác nhau:</t>
+  </si>
+  <si>
+    <t>CPU/SoC: thường cần điện áp thấp (0.8V – 1.2V)</t>
+  </si>
+  <si>
+    <t>RAM (DDR): khoảng 1.2V – 1.5V</t>
+  </si>
+  <si>
+    <t>IO (GPIO, UART, I2C...): thường 1.8V hoặc 3.3V</t>
+  </si>
+  <si>
+    <t>USB, Wi-Fi, màn hình, cảm biến...: mỗi thiết bị có yêu cầu riêng</t>
+  </si>
+  <si>
+    <r>
+      <t>Rail nguồn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Power Rail) là một đường cung cấp điện áp cụ thể cho các thành phần trên bo mạch. </t>
+    </r>
+  </si>
+  <si>
+    <t>Mỗi rail thường mang một điện áp riêng biệt và phục vụ một nhóm linh kiện cụ thể.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔢 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thứ tự cấp nguồn phổ biến (đối với SoC như ARM, i.MX, RK, STM32, etc.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Thứ tự</t>
+  </si>
+  <si>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>1️⃣</t>
+  </si>
+  <si>
+    <t>VDD_CORE / VDD_SOC</t>
+  </si>
+  <si>
+    <t>Nguồn lõi cho CPU/SoC</t>
+  </si>
+  <si>
+    <t>2️⃣</t>
+  </si>
+  <si>
+    <t>VDD_DDR</t>
+  </si>
+  <si>
+    <t>Nguồn cho RAM DDR</t>
+  </si>
+  <si>
+    <t>3️⃣</t>
+  </si>
+  <si>
+    <t>VDD_IO</t>
+  </si>
+  <si>
+    <t>Nguồn cho cổng giao tiếp ngoại vi (GPIO, UART...)</t>
+  </si>
+  <si>
+    <t>4️⃣</t>
+  </si>
+  <si>
+    <t>VDD_ANA / AVDD</t>
+  </si>
+  <si>
+    <t>Nguồn analog (ADC, DAC, audio...)</t>
+  </si>
+  <si>
+    <t>5️⃣</t>
+  </si>
+  <si>
+    <t>VCC_3V3 / VBUS / USB</t>
+  </si>
+  <si>
+    <t>Nguồn cho USB, module mở rộng</t>
+  </si>
+  <si>
+    <t>6️⃣</t>
+  </si>
+  <si>
+    <t>PERIPHERAL Power</t>
+  </si>
+  <si>
+    <t>Nguồn cảm biến, Wi-Fi, NAND, eMMC…</t>
+  </si>
+  <si>
+    <t>Cuối cùng</t>
+  </si>
+  <si>
+    <t>RESET_N / ENABLE</t>
+  </si>
+  <si>
+    <t>Kích hoạt SoC sau khi nguồn ổn định</t>
+  </si>
+  <si>
+    <t>BẢNG SO SÁNH CPU vs SoC</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>CPU (Central Processing Unit)</t>
+  </si>
+  <si>
+    <t>SoC (System on Chip)</t>
+  </si>
+  <si>
+    <t>Định nghĩa</t>
+  </si>
+  <si>
+    <t>Bộ xử lý trung tâm, thực hiện tính toán và điều khiển</t>
+  </si>
+  <si>
+    <t>Hệ thống tích hợp đầy đủ các thành phần (bao gồm CPU) trên một chip</t>
+  </si>
+  <si>
+    <t>Chức năng</t>
+  </si>
+  <si>
+    <t>Chỉ xử lý dữ liệu và điều khiển chương trình</t>
+  </si>
+  <si>
+    <t>Ngoài xử lý, còn bao gồm bộ nhớ, I/O, GPU, quản lý nguồn, ...</t>
+  </si>
+  <si>
+    <t>Thường chỉ có các nhân CPU (cores), cache, MMU</t>
+  </si>
+  <si>
+    <t>Kích thước vật lý</t>
+  </si>
+  <si>
+    <t>Lớn hơn, nhiều chân kết nối</t>
+  </si>
+  <si>
+    <t>Nhỏ gọn, thường dùng BGA, QFN, PoP</t>
+  </si>
+  <si>
+    <t>Nguồn điện</t>
+  </si>
+  <si>
+    <t>Cần nhiều nguồn cấp riêng biệt (core, IO, analog…)</t>
+  </si>
+  <si>
+    <t>Được thiết kế để tối ưu hóa nguồn trên hệ thống</t>
+  </si>
+  <si>
+    <t>Ứng dụng</t>
+  </si>
+  <si>
+    <t>PC, server, desktop, laptop</t>
+  </si>
+  <si>
+    <t>Thiết bị nhúng: điện thoại, router, camera, TV box, IoT, drone...</t>
+  </si>
+  <si>
+    <t>Ví dụ</t>
+  </si>
+  <si>
+    <t>Intel Core i7, AMD Ryzen 5</t>
+  </si>
+  <si>
+    <t>Qualcomm Snapdragon, NXP i.MX8, Allwinner A33, STM32F4</t>
+  </si>
+  <si>
+    <t>CPU + GPU + RAM controller + DMA + USB + I2C + UART + SPI + ...</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,8 +1053,68 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,8 +1139,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -619,11 +1279,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -641,12 +1338,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -689,10 +1380,102 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -710,6 +1493,117 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54AB2985-5EFE-1B7A-8532-EC7B16402E35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2857500" y="2981325"/>
+          <a:ext cx="8601075" cy="142875"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83D0FE25-CB55-4012-8821-00338FFAA6AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2571750" y="4600575"/>
+          <a:ext cx="7315200" cy="2200275"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1033,25 +1927,25 @@
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:71" ht="15" thickBot="1"/>
-    <row r="2" spans="1:71" s="11" customFormat="1" ht="24" thickBot="1">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="1:71" s="9" customFormat="1" ht="24" thickBot="1">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
     </row>
     <row r="4" spans="1:71" ht="17.25">
       <c r="B4" s="2" t="s">
@@ -1076,40 +1970,40 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7" t="s">
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="7"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-      <c r="AI5" s="7"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
       <c r="AL5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1132,77 +2026,77 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8" t="s">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="8"/>
-      <c r="AH6" s="8"/>
-      <c r="AI6" s="8"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
-      <c r="AP6" s="7" t="s">
+      <c r="AP6" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="AQ6" s="7"/>
-      <c r="AR6" s="7"/>
-      <c r="AS6" s="7"/>
-      <c r="AT6" s="7"/>
-      <c r="AU6" s="7"/>
-      <c r="AV6" s="7"/>
-      <c r="AW6" s="7"/>
-      <c r="AX6" s="7"/>
-      <c r="AY6" s="7"/>
-      <c r="AZ6" s="7"/>
-      <c r="BA6" s="7" t="s">
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="BB6" s="7"/>
-      <c r="BC6" s="7"/>
-      <c r="BD6" s="7"/>
-      <c r="BE6" s="7"/>
-      <c r="BF6" s="7"/>
-      <c r="BG6" s="7"/>
-      <c r="BH6" s="7"/>
-      <c r="BI6" s="7"/>
-      <c r="BJ6" s="7"/>
-      <c r="BK6" s="7"/>
-      <c r="BL6" s="7"/>
-      <c r="BM6" s="7"/>
-      <c r="BN6" s="7"/>
-      <c r="BO6" s="7"/>
-      <c r="BP6" s="7"/>
-      <c r="BQ6" s="7"/>
-      <c r="BR6" s="7"/>
-      <c r="BS6" s="7"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="27"/>
+      <c r="BL6" s="27"/>
+      <c r="BM6" s="27"/>
+      <c r="BN6" s="27"/>
+      <c r="BO6" s="27"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="27"/>
+      <c r="BS6" s="27"/>
     </row>
     <row r="7" spans="1:71">
       <c r="C7" s="4"/>
@@ -1284,40 +2178,40 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8" t="s">
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
       <c r="AM8" s="4"/>
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
@@ -1360,40 +2254,40 @@
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8" t="s">
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="8"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
       <c r="AM9" s="4"/>
       <c r="AN9" s="4"/>
       <c r="AO9" s="4"/>
@@ -1436,116 +2330,116 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8" t="s">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="8"/>
-      <c r="AI10" s="8"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="28"/>
+      <c r="AI10" s="28"/>
       <c r="AM10" s="4"/>
       <c r="AN10" s="4"/>
       <c r="AO10" s="4"/>
-      <c r="AP10" s="8" t="s">
+      <c r="AP10" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="AQ10" s="8"/>
-      <c r="AR10" s="8"/>
-      <c r="AS10" s="8"/>
-      <c r="AT10" s="8"/>
-      <c r="AU10" s="8"/>
-      <c r="AV10" s="8"/>
-      <c r="AW10" s="8"/>
-      <c r="AX10" s="8"/>
-      <c r="AY10" s="8"/>
-      <c r="AZ10" s="8"/>
-      <c r="BA10" s="8" t="s">
+      <c r="AQ10" s="28"/>
+      <c r="AR10" s="28"/>
+      <c r="AS10" s="28"/>
+      <c r="AT10" s="28"/>
+      <c r="AU10" s="28"/>
+      <c r="AV10" s="28"/>
+      <c r="AW10" s="28"/>
+      <c r="AX10" s="28"/>
+      <c r="AY10" s="28"/>
+      <c r="AZ10" s="28"/>
+      <c r="BA10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="BB10" s="8"/>
-      <c r="BC10" s="8"/>
-      <c r="BD10" s="8"/>
-      <c r="BE10" s="8"/>
-      <c r="BF10" s="8"/>
-      <c r="BG10" s="8"/>
-      <c r="BH10" s="8"/>
-      <c r="BI10" s="8"/>
-      <c r="BJ10" s="8"/>
-      <c r="BK10" s="8"/>
-      <c r="BL10" s="8"/>
-      <c r="BM10" s="8"/>
-      <c r="BN10" s="8"/>
-      <c r="BO10" s="8"/>
-      <c r="BP10" s="8"/>
-      <c r="BQ10" s="8"/>
-      <c r="BR10" s="8"/>
-      <c r="BS10" s="8"/>
+      <c r="BB10" s="28"/>
+      <c r="BC10" s="28"/>
+      <c r="BD10" s="28"/>
+      <c r="BE10" s="28"/>
+      <c r="BF10" s="28"/>
+      <c r="BG10" s="28"/>
+      <c r="BH10" s="28"/>
+      <c r="BI10" s="28"/>
+      <c r="BJ10" s="28"/>
+      <c r="BK10" s="28"/>
+      <c r="BL10" s="28"/>
+      <c r="BM10" s="28"/>
+      <c r="BN10" s="28"/>
+      <c r="BO10" s="28"/>
+      <c r="BP10" s="28"/>
+      <c r="BQ10" s="28"/>
+      <c r="BR10" s="28"/>
+      <c r="BS10" s="28"/>
     </row>
     <row r="11" spans="1:71">
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8" t="s">
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="28"/>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="28"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="28"/>
+      <c r="AH11" s="28"/>
+      <c r="AI11" s="28"/>
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
       <c r="AO11" s="4"/>
@@ -1588,40 +2482,40 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8" t="s">
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
+      <c r="AH12" s="28"/>
+      <c r="AI12" s="28"/>
     </row>
     <row r="15" spans="1:71" ht="17.25">
       <c r="B15" s="2" t="s">
@@ -1663,40 +2557,40 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7" t="s">
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="7"/>
-      <c r="AF16" s="7"/>
-      <c r="AG16" s="7"/>
-      <c r="AH16" s="7"/>
-      <c r="AI16" s="7"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27"/>
+      <c r="AH16" s="27"/>
+      <c r="AI16" s="27"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
@@ -1815,40 +2709,40 @@
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8" t="s">
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="8"/>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="8"/>
-      <c r="AH18" s="8"/>
-      <c r="AI18" s="8"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="28"/>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+      <c r="AH18" s="28"/>
+      <c r="AI18" s="28"/>
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
       <c r="AO18" s="4"/>
@@ -1891,40 +2785,40 @@
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8" t="s">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
-      <c r="AF19" s="8"/>
-      <c r="AG19" s="8"/>
-      <c r="AH19" s="8"/>
-      <c r="AI19" s="8"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="28"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="28"/>
+      <c r="AH19" s="28"/>
+      <c r="AI19" s="28"/>
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
@@ -1967,40 +2861,40 @@
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8" t="s">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AH20" s="8"/>
-      <c r="AI20" s="8"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AE20" s="28"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="28"/>
+      <c r="AH20" s="28"/>
+      <c r="AI20" s="28"/>
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
       <c r="AO20" s="4"/>
@@ -2043,40 +2937,40 @@
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8" t="s">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8"/>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8"/>
-      <c r="AE21" s="8"/>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="8"/>
-      <c r="AH21" s="8"/>
-      <c r="AI21" s="8"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28"/>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="28"/>
+      <c r="AA21" s="28"/>
+      <c r="AB21" s="28"/>
+      <c r="AC21" s="28"/>
+      <c r="AD21" s="28"/>
+      <c r="AE21" s="28"/>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="28"/>
+      <c r="AH21" s="28"/>
+      <c r="AI21" s="28"/>
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
       <c r="AO21" s="4"/>
@@ -2216,118 +3110,118 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7" t="s">
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
-      <c r="AD26" s="7"/>
-      <c r="AE26" s="7"/>
-      <c r="AF26" s="7"/>
-      <c r="AG26" s="7"/>
-      <c r="AH26" s="7"/>
-      <c r="AI26" s="7"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="27"/>
+      <c r="AD26" s="27"/>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="27"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="27"/>
+      <c r="AI26" s="27"/>
     </row>
     <row r="27" spans="1:71">
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8" t="s">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="8"/>
-      <c r="AF27" s="8"/>
-      <c r="AG27" s="8"/>
-      <c r="AH27" s="8"/>
-      <c r="AI27" s="8"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="28"/>
     </row>
     <row r="28" spans="1:71">
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8" t="s">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="8"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="8"/>
-      <c r="AF28" s="8"/>
-      <c r="AG28" s="8"/>
-      <c r="AH28" s="8"/>
-      <c r="AI28" s="8"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="28"/>
+      <c r="AE28" s="28"/>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="28"/>
+      <c r="AH28" s="28"/>
+      <c r="AI28" s="28"/>
     </row>
     <row r="29" spans="1:71">
       <c r="C29" s="4"/>
@@ -2372,424 +3266,424 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8" t="s">
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="8"/>
-      <c r="Z30" s="8"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="8"/>
-      <c r="AF30" s="8"/>
-      <c r="AG30" s="8"/>
-      <c r="AH30" s="8"/>
-      <c r="AI30" s="8"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
+      <c r="V30" s="28"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+      <c r="AC30" s="28"/>
+      <c r="AD30" s="28"/>
+      <c r="AE30" s="28"/>
+      <c r="AF30" s="28"/>
+      <c r="AG30" s="28"/>
+      <c r="AH30" s="28"/>
+      <c r="AI30" s="28"/>
     </row>
     <row r="31" spans="1:71" ht="15" thickBot="1"/>
-    <row r="32" spans="1:71" s="11" customFormat="1" ht="24" thickBot="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10" t="s">
+    <row r="32" spans="1:71" s="9" customFormat="1" ht="24" thickBot="1">
+      <c r="A32" s="7"/>
+      <c r="B32" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="34" spans="2:51" ht="17.25">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="13"/>
-      <c r="Q34" s="15"/>
-      <c r="S34" s="12" t="s">
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="13"/>
+      <c r="S34" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T34" s="13"/>
-      <c r="U34" s="13"/>
-      <c r="V34" s="13"/>
-      <c r="W34" s="13"/>
-      <c r="X34" s="13"/>
-      <c r="Y34" s="13"/>
-      <c r="Z34" s="13"/>
-      <c r="AA34" s="13"/>
-      <c r="AB34" s="13"/>
-      <c r="AC34" s="13"/>
-      <c r="AD34" s="13"/>
-      <c r="AE34" s="13"/>
-      <c r="AF34" s="13"/>
-      <c r="AG34" s="13"/>
-      <c r="AH34" s="15"/>
-      <c r="AK34" s="12" t="s">
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="11"/>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+      <c r="AD34" s="11"/>
+      <c r="AE34" s="11"/>
+      <c r="AF34" s="11"/>
+      <c r="AG34" s="11"/>
+      <c r="AH34" s="13"/>
+      <c r="AK34" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="AL34" s="13"/>
-      <c r="AM34" s="13"/>
-      <c r="AN34" s="13"/>
-      <c r="AO34" s="13"/>
-      <c r="AP34" s="13"/>
-      <c r="AQ34" s="13"/>
-      <c r="AR34" s="13"/>
-      <c r="AS34" s="13"/>
-      <c r="AT34" s="13"/>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="13"/>
-      <c r="AW34" s="13"/>
-      <c r="AX34" s="13"/>
-      <c r="AY34" s="24"/>
+      <c r="AL34" s="11"/>
+      <c r="AM34" s="11"/>
+      <c r="AN34" s="11"/>
+      <c r="AO34" s="11"/>
+      <c r="AP34" s="11"/>
+      <c r="AQ34" s="11"/>
+      <c r="AR34" s="11"/>
+      <c r="AS34" s="11"/>
+      <c r="AT34" s="11"/>
+      <c r="AU34" s="11"/>
+      <c r="AV34" s="11"/>
+      <c r="AW34" s="11"/>
+      <c r="AX34" s="11"/>
+      <c r="AY34" s="22"/>
     </row>
     <row r="35" spans="2:51">
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="19"/>
-      <c r="S35" s="16" t="s">
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="17"/>
+      <c r="S35" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-      <c r="AH35" s="19"/>
-      <c r="AK35" s="16" t="s">
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
+      <c r="AC35" s="15"/>
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="15"/>
+      <c r="AG35" s="15"/>
+      <c r="AH35" s="17"/>
+      <c r="AK35" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AL35" s="17"/>
-      <c r="AM35" s="17"/>
-      <c r="AN35" s="17"/>
-      <c r="AO35" s="17"/>
-      <c r="AP35" s="17"/>
-      <c r="AQ35" s="17"/>
-      <c r="AR35" s="17"/>
-      <c r="AS35" s="17"/>
-      <c r="AT35" s="17"/>
-      <c r="AU35" s="17"/>
-      <c r="AV35" s="17"/>
-      <c r="AW35" s="17"/>
-      <c r="AX35" s="17"/>
-      <c r="AY35" s="25"/>
+      <c r="AL35" s="15"/>
+      <c r="AM35" s="15"/>
+      <c r="AN35" s="15"/>
+      <c r="AO35" s="15"/>
+      <c r="AP35" s="15"/>
+      <c r="AQ35" s="15"/>
+      <c r="AR35" s="15"/>
+      <c r="AS35" s="15"/>
+      <c r="AT35" s="15"/>
+      <c r="AU35" s="15"/>
+      <c r="AV35" s="15"/>
+      <c r="AW35" s="15"/>
+      <c r="AX35" s="15"/>
+      <c r="AY35" s="23"/>
     </row>
     <row r="36" spans="2:51">
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="23"/>
-      <c r="S36" s="20" t="s">
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="21"/>
+      <c r="S36" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21"/>
-      <c r="X36" s="21"/>
-      <c r="Y36" s="21"/>
-      <c r="Z36" s="21"/>
-      <c r="AA36" s="21"/>
-      <c r="AB36" s="21"/>
-      <c r="AC36" s="21"/>
-      <c r="AD36" s="21"/>
-      <c r="AE36" s="21"/>
-      <c r="AF36" s="21"/>
-      <c r="AG36" s="21"/>
-      <c r="AH36" s="23"/>
-      <c r="AK36" s="20" t="s">
+      <c r="T36" s="19"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="19"/>
+      <c r="AA36" s="19"/>
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="19"/>
+      <c r="AD36" s="19"/>
+      <c r="AE36" s="19"/>
+      <c r="AF36" s="19"/>
+      <c r="AG36" s="19"/>
+      <c r="AH36" s="21"/>
+      <c r="AK36" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="AL36" s="21"/>
-      <c r="AM36" s="21"/>
-      <c r="AN36" s="21"/>
-      <c r="AO36" s="21"/>
-      <c r="AP36" s="21"/>
-      <c r="AQ36" s="21"/>
-      <c r="AR36" s="21"/>
-      <c r="AS36" s="21"/>
-      <c r="AT36" s="21"/>
-      <c r="AU36" s="21"/>
-      <c r="AV36" s="21"/>
-      <c r="AW36" s="21"/>
-      <c r="AX36" s="21"/>
-      <c r="AY36" s="26"/>
+      <c r="AL36" s="19"/>
+      <c r="AM36" s="19"/>
+      <c r="AN36" s="19"/>
+      <c r="AO36" s="19"/>
+      <c r="AP36" s="19"/>
+      <c r="AQ36" s="19"/>
+      <c r="AR36" s="19"/>
+      <c r="AS36" s="19"/>
+      <c r="AT36" s="19"/>
+      <c r="AU36" s="19"/>
+      <c r="AV36" s="19"/>
+      <c r="AW36" s="19"/>
+      <c r="AX36" s="19"/>
+      <c r="AY36" s="24"/>
     </row>
     <row r="38" spans="2:51" ht="17.25">
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="15"/>
-      <c r="S38" s="12" t="s">
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="13"/>
+      <c r="S38" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13"/>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="13"/>
-      <c r="AG38" s="13"/>
-      <c r="AH38" s="15"/>
-      <c r="AK38" s="12" t="s">
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11"/>
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="11"/>
+      <c r="AD38" s="11"/>
+      <c r="AE38" s="11"/>
+      <c r="AF38" s="11"/>
+      <c r="AG38" s="11"/>
+      <c r="AH38" s="13"/>
+      <c r="AK38" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AL38" s="13"/>
-      <c r="AM38" s="13"/>
-      <c r="AN38" s="13"/>
-      <c r="AO38" s="13"/>
-      <c r="AP38" s="13"/>
-      <c r="AQ38" s="13"/>
-      <c r="AR38" s="13"/>
-      <c r="AS38" s="13"/>
-      <c r="AT38" s="13"/>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="13"/>
-      <c r="AW38" s="13"/>
-      <c r="AX38" s="14"/>
-      <c r="AY38" s="15"/>
+      <c r="AL38" s="11"/>
+      <c r="AM38" s="11"/>
+      <c r="AN38" s="11"/>
+      <c r="AO38" s="11"/>
+      <c r="AP38" s="11"/>
+      <c r="AQ38" s="11"/>
+      <c r="AR38" s="11"/>
+      <c r="AS38" s="11"/>
+      <c r="AT38" s="11"/>
+      <c r="AU38" s="11"/>
+      <c r="AV38" s="11"/>
+      <c r="AW38" s="11"/>
+      <c r="AX38" s="12"/>
+      <c r="AY38" s="13"/>
     </row>
     <row r="39" spans="2:51">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
-      <c r="O39" s="17"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="19"/>
-      <c r="S39" s="16" t="s">
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="17"/>
+      <c r="S39" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="T39" s="17"/>
-      <c r="U39" s="17"/>
-      <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="17"/>
-      <c r="Y39" s="17"/>
-      <c r="Z39" s="17"/>
-      <c r="AA39" s="17"/>
-      <c r="AB39" s="17"/>
-      <c r="AC39" s="17"/>
-      <c r="AD39" s="17"/>
-      <c r="AE39" s="17"/>
-      <c r="AF39" s="17"/>
-      <c r="AG39" s="17"/>
-      <c r="AH39" s="19"/>
-      <c r="AK39" s="16" t="s">
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+      <c r="Z39" s="15"/>
+      <c r="AA39" s="15"/>
+      <c r="AB39" s="15"/>
+      <c r="AC39" s="15"/>
+      <c r="AD39" s="15"/>
+      <c r="AE39" s="15"/>
+      <c r="AF39" s="15"/>
+      <c r="AG39" s="15"/>
+      <c r="AH39" s="17"/>
+      <c r="AK39" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AL39" s="17"/>
-      <c r="AM39" s="17"/>
-      <c r="AN39" s="17"/>
-      <c r="AO39" s="17"/>
-      <c r="AP39" s="17"/>
-      <c r="AQ39" s="17"/>
-      <c r="AR39" s="17"/>
-      <c r="AS39" s="17"/>
-      <c r="AT39" s="17"/>
-      <c r="AU39" s="17"/>
-      <c r="AV39" s="17"/>
-      <c r="AW39" s="17"/>
-      <c r="AX39" s="18"/>
-      <c r="AY39" s="19"/>
+      <c r="AL39" s="15"/>
+      <c r="AM39" s="15"/>
+      <c r="AN39" s="15"/>
+      <c r="AO39" s="15"/>
+      <c r="AP39" s="15"/>
+      <c r="AQ39" s="15"/>
+      <c r="AR39" s="15"/>
+      <c r="AS39" s="15"/>
+      <c r="AT39" s="15"/>
+      <c r="AU39" s="15"/>
+      <c r="AV39" s="15"/>
+      <c r="AW39" s="15"/>
+      <c r="AX39" s="16"/>
+      <c r="AY39" s="17"/>
     </row>
     <row r="40" spans="2:51">
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="21"/>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="23"/>
-      <c r="S40" s="16" t="s">
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="21"/>
+      <c r="S40" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="T40" s="17"/>
-      <c r="U40" s="17"/>
-      <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="17"/>
-      <c r="Y40" s="17"/>
-      <c r="Z40" s="17"/>
-      <c r="AA40" s="17"/>
-      <c r="AB40" s="17"/>
-      <c r="AC40" s="17"/>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="17"/>
-      <c r="AF40" s="17"/>
-      <c r="AG40" s="17"/>
-      <c r="AH40" s="19"/>
-      <c r="AK40" s="27"/>
-      <c r="AL40" s="18"/>
-      <c r="AM40" s="18"/>
-      <c r="AN40" s="18"/>
-      <c r="AO40" s="18"/>
-      <c r="AP40" s="18"/>
-      <c r="AQ40" s="18"/>
-      <c r="AR40" s="18"/>
-      <c r="AS40" s="18"/>
-      <c r="AT40" s="18"/>
-      <c r="AU40" s="18"/>
-      <c r="AV40" s="18"/>
-      <c r="AW40" s="18"/>
-      <c r="AX40" s="18"/>
-      <c r="AY40" s="19"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+      <c r="Z40" s="15"/>
+      <c r="AA40" s="15"/>
+      <c r="AB40" s="15"/>
+      <c r="AC40" s="15"/>
+      <c r="AD40" s="15"/>
+      <c r="AE40" s="15"/>
+      <c r="AF40" s="15"/>
+      <c r="AG40" s="15"/>
+      <c r="AH40" s="17"/>
+      <c r="AK40" s="25"/>
+      <c r="AL40" s="16"/>
+      <c r="AM40" s="16"/>
+      <c r="AN40" s="16"/>
+      <c r="AO40" s="16"/>
+      <c r="AP40" s="16"/>
+      <c r="AQ40" s="16"/>
+      <c r="AR40" s="16"/>
+      <c r="AS40" s="16"/>
+      <c r="AT40" s="16"/>
+      <c r="AU40" s="16"/>
+      <c r="AV40" s="16"/>
+      <c r="AW40" s="16"/>
+      <c r="AX40" s="16"/>
+      <c r="AY40" s="17"/>
     </row>
     <row r="41" spans="2:51">
-      <c r="S41" s="20" t="s">
+      <c r="S41" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="T41" s="21"/>
-      <c r="U41" s="21"/>
-      <c r="V41" s="21"/>
-      <c r="W41" s="21"/>
-      <c r="X41" s="21"/>
-      <c r="Y41" s="21"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="21"/>
-      <c r="AB41" s="21"/>
-      <c r="AC41" s="21"/>
-      <c r="AD41" s="21"/>
-      <c r="AE41" s="21"/>
-      <c r="AF41" s="21"/>
-      <c r="AG41" s="21"/>
-      <c r="AH41" s="23"/>
-      <c r="AK41" s="28"/>
-      <c r="AL41" s="22"/>
-      <c r="AM41" s="22"/>
-      <c r="AN41" s="22"/>
-      <c r="AO41" s="22"/>
-      <c r="AP41" s="22"/>
-      <c r="AQ41" s="22"/>
-      <c r="AR41" s="22"/>
-      <c r="AS41" s="22"/>
-      <c r="AT41" s="22"/>
-      <c r="AU41" s="22"/>
-      <c r="AV41" s="22"/>
-      <c r="AW41" s="22"/>
-      <c r="AX41" s="22"/>
-      <c r="AY41" s="23"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="19"/>
+      <c r="AA41" s="19"/>
+      <c r="AB41" s="19"/>
+      <c r="AC41" s="19"/>
+      <c r="AD41" s="19"/>
+      <c r="AE41" s="19"/>
+      <c r="AF41" s="19"/>
+      <c r="AG41" s="19"/>
+      <c r="AH41" s="21"/>
+      <c r="AK41" s="26"/>
+      <c r="AL41" s="20"/>
+      <c r="AM41" s="20"/>
+      <c r="AN41" s="20"/>
+      <c r="AO41" s="20"/>
+      <c r="AP41" s="20"/>
+      <c r="AQ41" s="20"/>
+      <c r="AR41" s="20"/>
+      <c r="AS41" s="20"/>
+      <c r="AT41" s="20"/>
+      <c r="AU41" s="20"/>
+      <c r="AV41" s="20"/>
+      <c r="AW41" s="20"/>
+      <c r="AX41" s="20"/>
+      <c r="AY41" s="21"/>
     </row>
     <row r="46" spans="2:51" ht="17.25">
       <c r="P46" s="2"/>
@@ -3132,16 +4026,46 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:P26"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="F28:P28"/>
-    <mergeCell ref="F29:P29"/>
-    <mergeCell ref="F30:P30"/>
-    <mergeCell ref="Q26:AI26"/>
-    <mergeCell ref="Q27:AI27"/>
-    <mergeCell ref="Q28:AI28"/>
-    <mergeCell ref="Q29:AI29"/>
-    <mergeCell ref="Q30:AI30"/>
+    <mergeCell ref="F11:P11"/>
+    <mergeCell ref="F12:P12"/>
+    <mergeCell ref="Q5:AI5"/>
+    <mergeCell ref="Q6:AI6"/>
+    <mergeCell ref="Q7:AI7"/>
+    <mergeCell ref="Q8:AI8"/>
+    <mergeCell ref="Q9:AI9"/>
+    <mergeCell ref="Q10:AI10"/>
+    <mergeCell ref="Q11:AI11"/>
+    <mergeCell ref="Q12:AI12"/>
+    <mergeCell ref="F5:P5"/>
+    <mergeCell ref="F6:P6"/>
+    <mergeCell ref="F7:P7"/>
+    <mergeCell ref="F8:P8"/>
+    <mergeCell ref="F9:P9"/>
+    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="BA11:BS11"/>
+    <mergeCell ref="AP6:AZ6"/>
+    <mergeCell ref="AP7:AZ7"/>
+    <mergeCell ref="AP8:AZ8"/>
+    <mergeCell ref="AP9:AZ9"/>
+    <mergeCell ref="AP10:AZ10"/>
+    <mergeCell ref="AP11:AZ11"/>
+    <mergeCell ref="BA6:BS6"/>
+    <mergeCell ref="BA7:BS7"/>
+    <mergeCell ref="BA8:BS8"/>
+    <mergeCell ref="BA9:BS9"/>
+    <mergeCell ref="BA10:BS10"/>
+    <mergeCell ref="Q21:AI21"/>
+    <mergeCell ref="F16:P16"/>
+    <mergeCell ref="F17:P17"/>
+    <mergeCell ref="F18:P18"/>
+    <mergeCell ref="F19:P19"/>
+    <mergeCell ref="F20:P20"/>
+    <mergeCell ref="F21:P21"/>
+    <mergeCell ref="Q16:AI16"/>
+    <mergeCell ref="Q17:AI17"/>
+    <mergeCell ref="Q18:AI18"/>
+    <mergeCell ref="Q19:AI19"/>
+    <mergeCell ref="Q20:AI20"/>
     <mergeCell ref="AP22:AZ22"/>
     <mergeCell ref="AP23:AZ23"/>
     <mergeCell ref="BA16:BS16"/>
@@ -3158,46 +4082,16 @@
     <mergeCell ref="AP19:AZ19"/>
     <mergeCell ref="AP20:AZ20"/>
     <mergeCell ref="AP21:AZ21"/>
-    <mergeCell ref="Q16:AI16"/>
-    <mergeCell ref="Q17:AI17"/>
-    <mergeCell ref="Q18:AI18"/>
-    <mergeCell ref="Q19:AI19"/>
-    <mergeCell ref="Q20:AI20"/>
-    <mergeCell ref="Q21:AI21"/>
-    <mergeCell ref="F16:P16"/>
-    <mergeCell ref="F17:P17"/>
-    <mergeCell ref="F18:P18"/>
-    <mergeCell ref="F19:P19"/>
-    <mergeCell ref="F20:P20"/>
-    <mergeCell ref="F21:P21"/>
-    <mergeCell ref="BA6:BS6"/>
-    <mergeCell ref="BA7:BS7"/>
-    <mergeCell ref="BA8:BS8"/>
-    <mergeCell ref="BA9:BS9"/>
-    <mergeCell ref="BA10:BS10"/>
-    <mergeCell ref="BA11:BS11"/>
-    <mergeCell ref="AP6:AZ6"/>
-    <mergeCell ref="AP7:AZ7"/>
-    <mergeCell ref="AP8:AZ8"/>
-    <mergeCell ref="AP9:AZ9"/>
-    <mergeCell ref="AP10:AZ10"/>
-    <mergeCell ref="AP11:AZ11"/>
-    <mergeCell ref="F11:P11"/>
-    <mergeCell ref="F12:P12"/>
-    <mergeCell ref="Q5:AI5"/>
-    <mergeCell ref="Q6:AI6"/>
-    <mergeCell ref="Q7:AI7"/>
-    <mergeCell ref="Q8:AI8"/>
-    <mergeCell ref="Q9:AI9"/>
-    <mergeCell ref="Q10:AI10"/>
-    <mergeCell ref="Q11:AI11"/>
-    <mergeCell ref="Q12:AI12"/>
-    <mergeCell ref="F5:P5"/>
-    <mergeCell ref="F6:P6"/>
-    <mergeCell ref="F7:P7"/>
-    <mergeCell ref="F8:P8"/>
-    <mergeCell ref="F9:P9"/>
-    <mergeCell ref="F10:P10"/>
+    <mergeCell ref="Q26:AI26"/>
+    <mergeCell ref="Q27:AI27"/>
+    <mergeCell ref="Q28:AI28"/>
+    <mergeCell ref="Q29:AI29"/>
+    <mergeCell ref="Q30:AI30"/>
+    <mergeCell ref="F26:P26"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="F28:P28"/>
+    <mergeCell ref="F29:P29"/>
+    <mergeCell ref="F30:P30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3205,69 +4099,65 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4660090E-AC29-4380-AFFE-52F89CF83CCD}">
-  <dimension ref="A2:Y11"/>
+  <dimension ref="A2:CE79"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="2" spans="1:25" ht="15">
-      <c r="C2" s="7" t="s">
+    <row r="2" spans="1:70" ht="15">
+      <c r="C2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7" t="s">
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-    </row>
-    <row r="3" spans="1:25">
-      <c r="C3" s="8" t="s">
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+    </row>
+    <row r="3" spans="1:70">
+      <c r="C3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" t="s">
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:70">
       <c r="C4" s="29" t="s">
         <v>6</v>
       </c>
@@ -3292,194 +4182,2044 @@
       <c r="T4" s="29"/>
       <c r="U4" s="29"/>
       <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" t="s">
+      <c r="W4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
-      <c r="C5" s="8" t="s">
+    <row r="5" spans="1:70">
+      <c r="C5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8" t="s">
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" t="s">
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="C6" s="8" t="s">
+    <row r="6" spans="1:70">
+      <c r="C6" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="s">
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" t="s">
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="C7" s="8" t="s">
+    <row r="7" spans="1:70">
+      <c r="C7" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8" t="s">
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" t="s">
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="C8" s="8" t="s">
+    <row r="8" spans="1:70">
+      <c r="C8" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8" t="s">
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" t="s">
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
-      <c r="C9" s="8" t="s">
+    <row r="9" spans="1:70">
+      <c r="C9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8" t="s">
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" t="s">
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15" thickBot="1"/>
-    <row r="11" spans="1:25" s="11" customFormat="1" ht="15" thickBot="1">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11" t="s">
+    <row r="10" spans="1:70" ht="15" thickBot="1"/>
+    <row r="11" spans="1:70" s="9" customFormat="1" ht="15" thickBot="1">
+      <c r="A11" s="7"/>
+      <c r="B11" s="9" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="13" spans="1:70">
+      <c r="B13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" ht="18">
+      <c r="B14" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70" ht="15">
+      <c r="B15" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR15" s="38"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="39"/>
+      <c r="AZ15" s="39"/>
+      <c r="BA15" s="39"/>
+      <c r="BB15" s="39"/>
+      <c r="BC15" s="39"/>
+      <c r="BD15" s="39"/>
+      <c r="BE15" s="39"/>
+      <c r="BF15" s="39"/>
+      <c r="BG15" s="39"/>
+      <c r="BH15" s="39"/>
+      <c r="BI15" s="39"/>
+      <c r="BJ15" s="39"/>
+      <c r="BK15" s="39"/>
+      <c r="BL15" s="39"/>
+      <c r="BM15" s="39"/>
+      <c r="BN15" s="39"/>
+      <c r="BO15" s="39"/>
+      <c r="BP15" s="39"/>
+      <c r="BQ15" s="39"/>
+      <c r="BR15" s="40"/>
+    </row>
+    <row r="16" spans="1:70" ht="17.25">
+      <c r="B16" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="AT16" s="43"/>
+      <c r="AU16" s="43"/>
+      <c r="AV16" s="43"/>
+      <c r="AW16" s="43"/>
+      <c r="AX16" s="43"/>
+      <c r="AY16" s="43"/>
+      <c r="AZ16" s="43"/>
+      <c r="BA16" s="43"/>
+      <c r="BB16" s="43"/>
+      <c r="BC16" s="43"/>
+      <c r="BD16" s="43"/>
+      <c r="BE16" s="43"/>
+      <c r="BF16" s="43"/>
+      <c r="BG16" s="43"/>
+      <c r="BH16" s="43"/>
+      <c r="BI16" s="43"/>
+      <c r="BJ16" s="43"/>
+      <c r="BK16" s="43"/>
+      <c r="BL16" s="43"/>
+      <c r="BM16" s="43"/>
+      <c r="BN16" s="43"/>
+      <c r="BO16" s="43"/>
+      <c r="BP16" s="43"/>
+      <c r="BQ16" s="43"/>
+      <c r="BR16" s="44"/>
+    </row>
+    <row r="17" spans="2:70" ht="15">
+      <c r="B17" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR17" s="41"/>
+      <c r="AS17" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="AT17" s="43"/>
+      <c r="AU17" s="43"/>
+      <c r="AV17" s="43"/>
+      <c r="AW17" s="43"/>
+      <c r="AX17" s="43"/>
+      <c r="AY17" s="43"/>
+      <c r="AZ17" s="43"/>
+      <c r="BA17" s="43"/>
+      <c r="BB17" s="43"/>
+      <c r="BC17" s="43"/>
+      <c r="BD17" s="43"/>
+      <c r="BE17" s="43"/>
+      <c r="BF17" s="43"/>
+      <c r="BG17" s="43"/>
+      <c r="BH17" s="43"/>
+      <c r="BI17" s="43"/>
+      <c r="BJ17" s="43"/>
+      <c r="BK17" s="43"/>
+      <c r="BL17" s="43"/>
+      <c r="BM17" s="43"/>
+      <c r="BN17" s="43"/>
+      <c r="BO17" s="43"/>
+      <c r="BP17" s="43"/>
+      <c r="BQ17" s="43"/>
+      <c r="BR17" s="44"/>
+    </row>
+    <row r="18" spans="2:70">
+      <c r="B18" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR18" s="41"/>
+      <c r="AS18" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AT18" s="43"/>
+      <c r="AU18" s="43"/>
+      <c r="AV18" s="43"/>
+      <c r="AW18" s="43"/>
+      <c r="AX18" s="43"/>
+      <c r="AY18" s="43"/>
+      <c r="AZ18" s="43"/>
+      <c r="BA18" s="43"/>
+      <c r="BB18" s="43"/>
+      <c r="BC18" s="43"/>
+      <c r="BD18" s="43"/>
+      <c r="BE18" s="43"/>
+      <c r="BF18" s="43"/>
+      <c r="BG18" s="43"/>
+      <c r="BH18" s="43"/>
+      <c r="BI18" s="43"/>
+      <c r="BJ18" s="43"/>
+      <c r="BK18" s="43"/>
+      <c r="BL18" s="43"/>
+      <c r="BM18" s="43"/>
+      <c r="BN18" s="43"/>
+      <c r="BO18" s="43"/>
+      <c r="BP18" s="43"/>
+      <c r="BQ18" s="43"/>
+      <c r="BR18" s="44"/>
+    </row>
+    <row r="19" spans="2:70" ht="15">
+      <c r="B19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AR19" s="41"/>
+      <c r="AS19" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="AT19" s="46"/>
+      <c r="AU19" s="46"/>
+      <c r="AV19" s="46"/>
+      <c r="AW19" s="46"/>
+      <c r="AX19" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY19" s="46"/>
+      <c r="AZ19" s="46"/>
+      <c r="BA19" s="46"/>
+      <c r="BB19" s="46"/>
+      <c r="BC19" s="46"/>
+      <c r="BD19" s="46"/>
+      <c r="BE19" s="46"/>
+      <c r="BF19" s="46"/>
+      <c r="BG19" s="46"/>
+      <c r="BH19" s="46"/>
+      <c r="BI19" s="46"/>
+      <c r="BJ19" s="46"/>
+      <c r="BK19" s="46"/>
+      <c r="BL19" s="46"/>
+      <c r="BM19" s="46"/>
+      <c r="BN19" s="46"/>
+      <c r="BO19" s="46"/>
+      <c r="BP19" s="46"/>
+      <c r="BQ19" s="46"/>
+      <c r="BR19" s="44"/>
+    </row>
+    <row r="20" spans="2:70" ht="18">
+      <c r="B20" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR20" s="41"/>
+      <c r="AS20" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="AT20" s="47"/>
+      <c r="AU20" s="47"/>
+      <c r="AV20" s="47"/>
+      <c r="AW20" s="47"/>
+      <c r="AX20" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY20" s="47"/>
+      <c r="AZ20" s="47"/>
+      <c r="BA20" s="47"/>
+      <c r="BB20" s="47"/>
+      <c r="BC20" s="47"/>
+      <c r="BD20" s="47"/>
+      <c r="BE20" s="47"/>
+      <c r="BF20" s="47"/>
+      <c r="BG20" s="47"/>
+      <c r="BH20" s="47"/>
+      <c r="BI20" s="47"/>
+      <c r="BJ20" s="47"/>
+      <c r="BK20" s="47"/>
+      <c r="BL20" s="47"/>
+      <c r="BM20" s="47"/>
+      <c r="BN20" s="47"/>
+      <c r="BO20" s="47"/>
+      <c r="BP20" s="47"/>
+      <c r="BQ20" s="47"/>
+      <c r="BR20" s="44"/>
+    </row>
+    <row r="21" spans="2:70">
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="AR21" s="41"/>
+      <c r="AS21" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="AT21" s="47"/>
+      <c r="AU21" s="47"/>
+      <c r="AV21" s="47"/>
+      <c r="AW21" s="47"/>
+      <c r="AX21" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY21" s="47"/>
+      <c r="AZ21" s="47"/>
+      <c r="BA21" s="47"/>
+      <c r="BB21" s="47"/>
+      <c r="BC21" s="47"/>
+      <c r="BD21" s="47"/>
+      <c r="BE21" s="47"/>
+      <c r="BF21" s="47"/>
+      <c r="BG21" s="47"/>
+      <c r="BH21" s="47"/>
+      <c r="BI21" s="47"/>
+      <c r="BJ21" s="47"/>
+      <c r="BK21" s="47"/>
+      <c r="BL21" s="47"/>
+      <c r="BM21" s="47"/>
+      <c r="BN21" s="47"/>
+      <c r="BO21" s="47"/>
+      <c r="BP21" s="47"/>
+      <c r="BQ21" s="47"/>
+      <c r="BR21" s="44"/>
+    </row>
+    <row r="22" spans="2:70" ht="17.25">
+      <c r="B22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AR22" s="41"/>
+      <c r="AS22" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="AT22" s="47"/>
+      <c r="AU22" s="47"/>
+      <c r="AV22" s="47"/>
+      <c r="AW22" s="47"/>
+      <c r="AX22" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY22" s="47"/>
+      <c r="AZ22" s="47"/>
+      <c r="BA22" s="47"/>
+      <c r="BB22" s="47"/>
+      <c r="BC22" s="47"/>
+      <c r="BD22" s="47"/>
+      <c r="BE22" s="47"/>
+      <c r="BF22" s="47"/>
+      <c r="BG22" s="47"/>
+      <c r="BH22" s="47"/>
+      <c r="BI22" s="47"/>
+      <c r="BJ22" s="47"/>
+      <c r="BK22" s="47"/>
+      <c r="BL22" s="47"/>
+      <c r="BM22" s="47"/>
+      <c r="BN22" s="47"/>
+      <c r="BO22" s="47"/>
+      <c r="BP22" s="47"/>
+      <c r="BQ22" s="47"/>
+      <c r="BR22" s="44"/>
+    </row>
+    <row r="23" spans="2:70" ht="15">
+      <c r="B23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR23" s="41"/>
+      <c r="AS23" s="43"/>
+      <c r="AT23" s="43"/>
+      <c r="AU23" s="43"/>
+      <c r="AV23" s="43"/>
+      <c r="AW23" s="43"/>
+      <c r="AX23" s="43"/>
+      <c r="AY23" s="43"/>
+      <c r="AZ23" s="43"/>
+      <c r="BA23" s="43"/>
+      <c r="BB23" s="43"/>
+      <c r="BC23" s="43"/>
+      <c r="BD23" s="43"/>
+      <c r="BE23" s="43"/>
+      <c r="BF23" s="43"/>
+      <c r="BG23" s="43"/>
+      <c r="BH23" s="43"/>
+      <c r="BI23" s="43"/>
+      <c r="BJ23" s="43"/>
+      <c r="BK23" s="43"/>
+      <c r="BL23" s="43"/>
+      <c r="BM23" s="43"/>
+      <c r="BN23" s="43"/>
+      <c r="BO23" s="43"/>
+      <c r="BP23" s="43"/>
+      <c r="BQ23" s="43"/>
+      <c r="BR23" s="44"/>
+    </row>
+    <row r="24" spans="2:70" ht="18.75" customHeight="1">
+      <c r="B24" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR24" s="41"/>
+      <c r="AS24" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="AT24" s="43"/>
+      <c r="AU24" s="43"/>
+      <c r="AV24" s="43"/>
+      <c r="AW24" s="43"/>
+      <c r="AX24" s="43"/>
+      <c r="AY24" s="43"/>
+      <c r="AZ24" s="43"/>
+      <c r="BA24" s="43"/>
+      <c r="BB24" s="43"/>
+      <c r="BC24" s="43"/>
+      <c r="BD24" s="43"/>
+      <c r="BE24" s="43"/>
+      <c r="BF24" s="43"/>
+      <c r="BG24" s="43"/>
+      <c r="BH24" s="43"/>
+      <c r="BI24" s="43"/>
+      <c r="BJ24" s="43"/>
+      <c r="BK24" s="43"/>
+      <c r="BL24" s="43"/>
+      <c r="BM24" s="43"/>
+      <c r="BN24" s="43"/>
+      <c r="BO24" s="43"/>
+      <c r="BP24" s="43"/>
+      <c r="BQ24" s="43"/>
+      <c r="BR24" s="44"/>
+    </row>
+    <row r="25" spans="2:70" ht="17.25">
+      <c r="B25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR25" s="41"/>
+      <c r="AS25" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="AT25" s="43"/>
+      <c r="AU25" s="43"/>
+      <c r="AV25" s="43"/>
+      <c r="AW25" s="43"/>
+      <c r="AX25" s="43"/>
+      <c r="AY25" s="43"/>
+      <c r="AZ25" s="43"/>
+      <c r="BA25" s="43"/>
+      <c r="BB25" s="43"/>
+      <c r="BC25" s="43"/>
+      <c r="BD25" s="43"/>
+      <c r="BE25" s="43"/>
+      <c r="BF25" s="43"/>
+      <c r="BG25" s="43"/>
+      <c r="BH25" s="43"/>
+      <c r="BI25" s="43"/>
+      <c r="BJ25" s="43"/>
+      <c r="BK25" s="43"/>
+      <c r="BL25" s="43"/>
+      <c r="BM25" s="43"/>
+      <c r="BN25" s="43"/>
+      <c r="BO25" s="43"/>
+      <c r="BP25" s="43"/>
+      <c r="BQ25" s="43"/>
+      <c r="BR25" s="44"/>
+    </row>
+    <row r="26" spans="2:70" ht="15">
+      <c r="B26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR26" s="41"/>
+      <c r="AS26" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT26" s="39"/>
+      <c r="AU26" s="39"/>
+      <c r="AV26" s="39"/>
+      <c r="AW26" s="39"/>
+      <c r="AX26" s="39"/>
+      <c r="AY26" s="39"/>
+      <c r="AZ26" s="39"/>
+      <c r="BA26" s="39"/>
+      <c r="BB26" s="39"/>
+      <c r="BC26" s="39"/>
+      <c r="BD26" s="39"/>
+      <c r="BE26" s="39"/>
+      <c r="BF26" s="39"/>
+      <c r="BG26" s="39"/>
+      <c r="BH26" s="39"/>
+      <c r="BI26" s="39"/>
+      <c r="BJ26" s="39"/>
+      <c r="BK26" s="40"/>
+      <c r="BL26" s="43"/>
+      <c r="BM26" s="43"/>
+      <c r="BN26" s="43"/>
+      <c r="BO26" s="43"/>
+      <c r="BP26" s="43"/>
+      <c r="BQ26" s="43"/>
+      <c r="BR26" s="44"/>
+    </row>
+    <row r="27" spans="2:70" ht="15">
+      <c r="B27" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="AR27" s="41"/>
+      <c r="AS27" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT27" s="43"/>
+      <c r="AU27" s="43"/>
+      <c r="AV27" s="43"/>
+      <c r="AW27" s="43"/>
+      <c r="AX27" s="43"/>
+      <c r="AY27" s="43"/>
+      <c r="AZ27" s="43"/>
+      <c r="BA27" s="43"/>
+      <c r="BB27" s="43"/>
+      <c r="BC27" s="43"/>
+      <c r="BD27" s="43"/>
+      <c r="BE27" s="43"/>
+      <c r="BF27" s="43"/>
+      <c r="BG27" s="43"/>
+      <c r="BH27" s="43"/>
+      <c r="BI27" s="43"/>
+      <c r="BJ27" s="43"/>
+      <c r="BK27" s="44"/>
+      <c r="BL27" s="43"/>
+      <c r="BM27" s="43"/>
+      <c r="BN27" s="43"/>
+      <c r="BO27" s="43"/>
+      <c r="BP27" s="43"/>
+      <c r="BQ27" s="43"/>
+      <c r="BR27" s="44"/>
+    </row>
+    <row r="28" spans="2:70">
+      <c r="B28" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR28" s="41"/>
+      <c r="AS28" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="AT28" s="43"/>
+      <c r="AU28" s="43"/>
+      <c r="AV28" s="43"/>
+      <c r="AW28" s="43"/>
+      <c r="AX28" s="43"/>
+      <c r="AY28" s="43"/>
+      <c r="AZ28" s="43"/>
+      <c r="BA28" s="43"/>
+      <c r="BB28" s="43"/>
+      <c r="BC28" s="43"/>
+      <c r="BD28" s="43"/>
+      <c r="BE28" s="43"/>
+      <c r="BF28" s="43"/>
+      <c r="BG28" s="43"/>
+      <c r="BH28" s="43"/>
+      <c r="BI28" s="43"/>
+      <c r="BJ28" s="43"/>
+      <c r="BK28" s="44"/>
+      <c r="BL28" s="43"/>
+      <c r="BM28" s="43"/>
+      <c r="BN28" s="43"/>
+      <c r="BO28" s="43"/>
+      <c r="BP28" s="43"/>
+      <c r="BQ28" s="43"/>
+      <c r="BR28" s="44"/>
+    </row>
+    <row r="29" spans="2:70">
+      <c r="B29" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR29" s="41"/>
+      <c r="AS29" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="49"/>
+      <c r="AV29" s="49"/>
+      <c r="AW29" s="49"/>
+      <c r="AX29" s="49"/>
+      <c r="AY29" s="49"/>
+      <c r="AZ29" s="49"/>
+      <c r="BA29" s="49"/>
+      <c r="BB29" s="49"/>
+      <c r="BC29" s="49"/>
+      <c r="BD29" s="49"/>
+      <c r="BE29" s="49"/>
+      <c r="BF29" s="49"/>
+      <c r="BG29" s="49"/>
+      <c r="BH29" s="49"/>
+      <c r="BI29" s="49"/>
+      <c r="BJ29" s="49"/>
+      <c r="BK29" s="50"/>
+      <c r="BL29" s="43"/>
+      <c r="BM29" s="43"/>
+      <c r="BN29" s="43"/>
+      <c r="BO29" s="43"/>
+      <c r="BP29" s="43"/>
+      <c r="BQ29" s="43"/>
+      <c r="BR29" s="44"/>
+    </row>
+    <row r="30" spans="2:70">
+      <c r="B30" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR30" s="48"/>
+      <c r="AS30" s="49"/>
+      <c r="AT30" s="49"/>
+      <c r="AU30" s="49"/>
+      <c r="AV30" s="49"/>
+      <c r="AW30" s="49"/>
+      <c r="AX30" s="49"/>
+      <c r="AY30" s="49"/>
+      <c r="AZ30" s="49"/>
+      <c r="BA30" s="49"/>
+      <c r="BB30" s="49"/>
+      <c r="BC30" s="49"/>
+      <c r="BD30" s="49"/>
+      <c r="BE30" s="49"/>
+      <c r="BF30" s="49"/>
+      <c r="BG30" s="49"/>
+      <c r="BH30" s="49"/>
+      <c r="BI30" s="49"/>
+      <c r="BJ30" s="49"/>
+      <c r="BK30" s="49"/>
+      <c r="BL30" s="49"/>
+      <c r="BM30" s="49"/>
+      <c r="BN30" s="49"/>
+      <c r="BO30" s="49"/>
+      <c r="BP30" s="49"/>
+      <c r="BQ30" s="49"/>
+      <c r="BR30" s="50"/>
+    </row>
+    <row r="31" spans="2:70" ht="17.25">
+      <c r="B31" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:70">
+      <c r="B32" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AQ32" s="38"/>
+      <c r="AR32" s="39"/>
+      <c r="AS32" s="39"/>
+      <c r="AT32" s="39"/>
+      <c r="AU32" s="39"/>
+      <c r="AV32" s="39"/>
+      <c r="AW32" s="39"/>
+      <c r="AX32" s="39"/>
+      <c r="AY32" s="39"/>
+      <c r="AZ32" s="39"/>
+      <c r="BA32" s="39"/>
+      <c r="BB32" s="39"/>
+      <c r="BC32" s="39"/>
+      <c r="BD32" s="39"/>
+      <c r="BE32" s="39"/>
+      <c r="BF32" s="39"/>
+      <c r="BG32" s="39"/>
+      <c r="BH32" s="39"/>
+      <c r="BI32" s="39"/>
+      <c r="BJ32" s="39"/>
+      <c r="BK32" s="39"/>
+      <c r="BL32" s="39"/>
+      <c r="BM32" s="39"/>
+      <c r="BN32" s="39"/>
+      <c r="BO32" s="39"/>
+      <c r="BP32" s="40"/>
+    </row>
+    <row r="33" spans="2:68" ht="15">
+      <c r="B33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AQ33" s="41"/>
+      <c r="AR33" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AS33" s="43"/>
+      <c r="AT33" s="43"/>
+      <c r="AU33" s="43"/>
+      <c r="AV33" s="43"/>
+      <c r="AW33" s="43"/>
+      <c r="AX33" s="43"/>
+      <c r="AY33" s="43"/>
+      <c r="AZ33" s="43"/>
+      <c r="BA33" s="43"/>
+      <c r="BB33" s="43"/>
+      <c r="BC33" s="43"/>
+      <c r="BD33" s="43"/>
+      <c r="BE33" s="43"/>
+      <c r="BF33" s="43"/>
+      <c r="BG33" s="43"/>
+      <c r="BH33" s="43"/>
+      <c r="BI33" s="43"/>
+      <c r="BJ33" s="43"/>
+      <c r="BK33" s="43"/>
+      <c r="BL33" s="43"/>
+      <c r="BM33" s="43"/>
+      <c r="BN33" s="43"/>
+      <c r="BO33" s="43"/>
+      <c r="BP33" s="44"/>
+    </row>
+    <row r="34" spans="2:68" ht="17.25">
+      <c r="B34" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AQ34" s="41"/>
+      <c r="AR34" s="43"/>
+      <c r="AS34" s="43"/>
+      <c r="AT34" s="43"/>
+      <c r="AU34" s="43"/>
+      <c r="AV34" s="43"/>
+      <c r="AW34" s="43"/>
+      <c r="AX34" s="43"/>
+      <c r="AY34" s="43"/>
+      <c r="AZ34" s="43"/>
+      <c r="BA34" s="43"/>
+      <c r="BB34" s="43"/>
+      <c r="BC34" s="43"/>
+      <c r="BD34" s="43"/>
+      <c r="BE34" s="43"/>
+      <c r="BF34" s="43"/>
+      <c r="BG34" s="43"/>
+      <c r="BH34" s="43"/>
+      <c r="BI34" s="43"/>
+      <c r="BJ34" s="43"/>
+      <c r="BK34" s="43"/>
+      <c r="BL34" s="43"/>
+      <c r="BM34" s="43"/>
+      <c r="BN34" s="43"/>
+      <c r="BO34" s="43"/>
+      <c r="BP34" s="44"/>
+    </row>
+    <row r="35" spans="2:68" ht="15">
+      <c r="B35" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ35" s="41"/>
+      <c r="AR35" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS35" s="46"/>
+      <c r="AT35" s="46"/>
+      <c r="AU35" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV35" s="46"/>
+      <c r="AW35" s="46"/>
+      <c r="AX35" s="46"/>
+      <c r="AY35" s="46"/>
+      <c r="AZ35" s="46"/>
+      <c r="BA35" s="46"/>
+      <c r="BB35" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC35" s="46"/>
+      <c r="BD35" s="46"/>
+      <c r="BE35" s="46"/>
+      <c r="BF35" s="46"/>
+      <c r="BG35" s="46"/>
+      <c r="BH35" s="46"/>
+      <c r="BI35" s="46"/>
+      <c r="BJ35" s="46"/>
+      <c r="BK35" s="46"/>
+      <c r="BL35" s="46"/>
+      <c r="BM35" s="46"/>
+      <c r="BN35" s="46"/>
+      <c r="BO35" s="46"/>
+      <c r="BP35" s="44"/>
+    </row>
+    <row r="36" spans="2:68" ht="15">
+      <c r="B36" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ36" s="41"/>
+      <c r="AR36" s="56" t="s">
+        <v>168</v>
+      </c>
+      <c r="AS36" s="56"/>
+      <c r="AT36" s="56"/>
+      <c r="AU36" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="AV36" s="57"/>
+      <c r="AW36" s="57"/>
+      <c r="AX36" s="57"/>
+      <c r="AY36" s="57"/>
+      <c r="AZ36" s="57"/>
+      <c r="BA36" s="57"/>
+      <c r="BB36" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="BC36" s="47"/>
+      <c r="BD36" s="47"/>
+      <c r="BE36" s="47"/>
+      <c r="BF36" s="47"/>
+      <c r="BG36" s="47"/>
+      <c r="BH36" s="47"/>
+      <c r="BI36" s="47"/>
+      <c r="BJ36" s="47"/>
+      <c r="BK36" s="47"/>
+      <c r="BL36" s="47"/>
+      <c r="BM36" s="47"/>
+      <c r="BN36" s="47"/>
+      <c r="BO36" s="47"/>
+      <c r="BP36" s="44"/>
+    </row>
+    <row r="37" spans="2:68" ht="17.25">
+      <c r="B37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AQ37" s="41"/>
+      <c r="AR37" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="AS37" s="56"/>
+      <c r="AT37" s="56"/>
+      <c r="AU37" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="AV37" s="57"/>
+      <c r="AW37" s="57"/>
+      <c r="AX37" s="57"/>
+      <c r="AY37" s="57"/>
+      <c r="AZ37" s="57"/>
+      <c r="BA37" s="57"/>
+      <c r="BB37" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="BC37" s="47"/>
+      <c r="BD37" s="47"/>
+      <c r="BE37" s="47"/>
+      <c r="BF37" s="47"/>
+      <c r="BG37" s="47"/>
+      <c r="BH37" s="47"/>
+      <c r="BI37" s="47"/>
+      <c r="BJ37" s="47"/>
+      <c r="BK37" s="47"/>
+      <c r="BL37" s="47"/>
+      <c r="BM37" s="47"/>
+      <c r="BN37" s="47"/>
+      <c r="BO37" s="47"/>
+      <c r="BP37" s="44"/>
+    </row>
+    <row r="38" spans="2:68" ht="15">
+      <c r="B38" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ38" s="41"/>
+      <c r="AR38" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="AS38" s="56"/>
+      <c r="AT38" s="56"/>
+      <c r="AU38" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="AV38" s="57"/>
+      <c r="AW38" s="57"/>
+      <c r="AX38" s="57"/>
+      <c r="AY38" s="57"/>
+      <c r="AZ38" s="57"/>
+      <c r="BA38" s="57"/>
+      <c r="BB38" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="BC38" s="47"/>
+      <c r="BD38" s="47"/>
+      <c r="BE38" s="47"/>
+      <c r="BF38" s="47"/>
+      <c r="BG38" s="47"/>
+      <c r="BH38" s="47"/>
+      <c r="BI38" s="47"/>
+      <c r="BJ38" s="47"/>
+      <c r="BK38" s="47"/>
+      <c r="BL38" s="47"/>
+      <c r="BM38" s="47"/>
+      <c r="BN38" s="47"/>
+      <c r="BO38" s="47"/>
+      <c r="BP38" s="44"/>
+    </row>
+    <row r="39" spans="2:68" ht="15">
+      <c r="B39" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ39" s="41"/>
+      <c r="AR39" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS39" s="56"/>
+      <c r="AT39" s="56"/>
+      <c r="AU39" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="AV39" s="57"/>
+      <c r="AW39" s="57"/>
+      <c r="AX39" s="57"/>
+      <c r="AY39" s="57"/>
+      <c r="AZ39" s="57"/>
+      <c r="BA39" s="57"/>
+      <c r="BB39" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="BC39" s="47"/>
+      <c r="BD39" s="47"/>
+      <c r="BE39" s="47"/>
+      <c r="BF39" s="47"/>
+      <c r="BG39" s="47"/>
+      <c r="BH39" s="47"/>
+      <c r="BI39" s="47"/>
+      <c r="BJ39" s="47"/>
+      <c r="BK39" s="47"/>
+      <c r="BL39" s="47"/>
+      <c r="BM39" s="47"/>
+      <c r="BN39" s="47"/>
+      <c r="BO39" s="47"/>
+      <c r="BP39" s="44"/>
+    </row>
+    <row r="40" spans="2:68" ht="15">
+      <c r="AQ40" s="41"/>
+      <c r="AR40" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="AS40" s="56"/>
+      <c r="AT40" s="56"/>
+      <c r="AU40" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="AV40" s="57"/>
+      <c r="AW40" s="57"/>
+      <c r="AX40" s="57"/>
+      <c r="AY40" s="57"/>
+      <c r="AZ40" s="57"/>
+      <c r="BA40" s="57"/>
+      <c r="BB40" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="BC40" s="47"/>
+      <c r="BD40" s="47"/>
+      <c r="BE40" s="47"/>
+      <c r="BF40" s="47"/>
+      <c r="BG40" s="47"/>
+      <c r="BH40" s="47"/>
+      <c r="BI40" s="47"/>
+      <c r="BJ40" s="47"/>
+      <c r="BK40" s="47"/>
+      <c r="BL40" s="47"/>
+      <c r="BM40" s="47"/>
+      <c r="BN40" s="47"/>
+      <c r="BO40" s="47"/>
+      <c r="BP40" s="44"/>
+    </row>
+    <row r="41" spans="2:68" ht="15">
+      <c r="AQ41" s="41"/>
+      <c r="AR41" s="56" t="s">
+        <v>183</v>
+      </c>
+      <c r="AS41" s="56"/>
+      <c r="AT41" s="56"/>
+      <c r="AU41" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="AV41" s="57"/>
+      <c r="AW41" s="57"/>
+      <c r="AX41" s="57"/>
+      <c r="AY41" s="57"/>
+      <c r="AZ41" s="57"/>
+      <c r="BA41" s="57"/>
+      <c r="BB41" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="BC41" s="47"/>
+      <c r="BD41" s="47"/>
+      <c r="BE41" s="47"/>
+      <c r="BF41" s="47"/>
+      <c r="BG41" s="47"/>
+      <c r="BH41" s="47"/>
+      <c r="BI41" s="47"/>
+      <c r="BJ41" s="47"/>
+      <c r="BK41" s="47"/>
+      <c r="BL41" s="47"/>
+      <c r="BM41" s="47"/>
+      <c r="BN41" s="47"/>
+      <c r="BO41" s="47"/>
+      <c r="BP41" s="44"/>
+    </row>
+    <row r="42" spans="2:68" ht="15" customHeight="1">
+      <c r="D42" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="65"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="66"/>
+      <c r="M42" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="N42" s="65"/>
+      <c r="O42" s="65"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="66"/>
+      <c r="AQ42" s="41"/>
+      <c r="AR42" s="56" t="s">
+        <v>186</v>
+      </c>
+      <c r="AS42" s="56"/>
+      <c r="AT42" s="56"/>
+      <c r="AU42" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="AV42" s="57"/>
+      <c r="AW42" s="57"/>
+      <c r="AX42" s="57"/>
+      <c r="AY42" s="57"/>
+      <c r="AZ42" s="57"/>
+      <c r="BA42" s="57"/>
+      <c r="BB42" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="BC42" s="47"/>
+      <c r="BD42" s="47"/>
+      <c r="BE42" s="47"/>
+      <c r="BF42" s="47"/>
+      <c r="BG42" s="47"/>
+      <c r="BH42" s="47"/>
+      <c r="BI42" s="47"/>
+      <c r="BJ42" s="47"/>
+      <c r="BK42" s="47"/>
+      <c r="BL42" s="47"/>
+      <c r="BM42" s="47"/>
+      <c r="BN42" s="47"/>
+      <c r="BO42" s="47"/>
+      <c r="BP42" s="44"/>
+    </row>
+    <row r="43" spans="2:68" ht="14.25" customHeight="1">
+      <c r="D43" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="62"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="J43" s="62"/>
+      <c r="K43" s="62"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="N43" s="62"/>
+      <c r="O43" s="62"/>
+      <c r="P43" s="62"/>
+      <c r="Q43" s="62"/>
+      <c r="R43" s="62"/>
+      <c r="S43" s="63"/>
+      <c r="AQ43" s="41"/>
+      <c r="AR43" s="43"/>
+      <c r="AS43" s="43"/>
+      <c r="AT43" s="43"/>
+      <c r="AU43" s="43"/>
+      <c r="AV43" s="43"/>
+      <c r="AW43" s="43"/>
+      <c r="AX43" s="43"/>
+      <c r="AY43" s="43"/>
+      <c r="AZ43" s="43"/>
+      <c r="BA43" s="43"/>
+      <c r="BB43" s="43"/>
+      <c r="BC43" s="43"/>
+      <c r="BD43" s="43"/>
+      <c r="BE43" s="43"/>
+      <c r="BF43" s="43"/>
+      <c r="BG43" s="43"/>
+      <c r="BH43" s="43"/>
+      <c r="BI43" s="43"/>
+      <c r="BJ43" s="43"/>
+      <c r="BK43" s="43"/>
+      <c r="BL43" s="43"/>
+      <c r="BM43" s="43"/>
+      <c r="BN43" s="43"/>
+      <c r="BO43" s="43"/>
+      <c r="BP43" s="44"/>
+    </row>
+    <row r="44" spans="2:68" ht="14.25" customHeight="1">
+      <c r="D44" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="62"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
+      <c r="J44" s="62"/>
+      <c r="K44" s="62"/>
+      <c r="L44" s="63"/>
+      <c r="M44" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="N44" s="62"/>
+      <c r="O44" s="62"/>
+      <c r="P44" s="62"/>
+      <c r="Q44" s="62"/>
+      <c r="R44" s="62"/>
+      <c r="S44" s="63"/>
+      <c r="AQ44" s="41"/>
+      <c r="AR44" s="43"/>
+      <c r="AS44" s="43"/>
+      <c r="AT44" s="43"/>
+      <c r="AU44" s="43"/>
+      <c r="AV44" s="43"/>
+      <c r="AW44" s="43"/>
+      <c r="AX44" s="43"/>
+      <c r="AY44" s="43"/>
+      <c r="AZ44" s="43"/>
+      <c r="BA44" s="43"/>
+      <c r="BB44" s="43"/>
+      <c r="BC44" s="43"/>
+      <c r="BD44" s="43"/>
+      <c r="BE44" s="43"/>
+      <c r="BF44" s="43"/>
+      <c r="BG44" s="43"/>
+      <c r="BH44" s="43"/>
+      <c r="BI44" s="43"/>
+      <c r="BJ44" s="43"/>
+      <c r="BK44" s="43"/>
+      <c r="BL44" s="43"/>
+      <c r="BM44" s="43"/>
+      <c r="BN44" s="43"/>
+      <c r="BO44" s="43"/>
+      <c r="BP44" s="44"/>
+    </row>
+    <row r="45" spans="2:68" ht="14.25" customHeight="1">
+      <c r="D45" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="62"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="H45" s="62"/>
+      <c r="I45" s="62"/>
+      <c r="J45" s="62"/>
+      <c r="K45" s="62"/>
+      <c r="L45" s="63"/>
+      <c r="M45" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="N45" s="62"/>
+      <c r="O45" s="62"/>
+      <c r="P45" s="62"/>
+      <c r="Q45" s="62"/>
+      <c r="R45" s="62"/>
+      <c r="S45" s="63"/>
+      <c r="AQ45" s="48"/>
+      <c r="AR45" s="49"/>
+      <c r="AS45" s="49"/>
+      <c r="AT45" s="49"/>
+      <c r="AU45" s="49"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
+      <c r="BB45" s="49"/>
+      <c r="BC45" s="49"/>
+      <c r="BD45" s="49"/>
+      <c r="BE45" s="49"/>
+      <c r="BF45" s="49"/>
+      <c r="BG45" s="49"/>
+      <c r="BH45" s="49"/>
+      <c r="BI45" s="49"/>
+      <c r="BJ45" s="49"/>
+      <c r="BK45" s="49"/>
+      <c r="BL45" s="49"/>
+      <c r="BM45" s="49"/>
+      <c r="BN45" s="49"/>
+      <c r="BO45" s="49"/>
+      <c r="BP45" s="50"/>
+    </row>
+    <row r="46" spans="2:68">
+      <c r="D46" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+    </row>
+    <row r="49" spans="2:83" ht="23.25">
+      <c r="B49" s="1"/>
+      <c r="D49" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27"/>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="O49" s="27"/>
+      <c r="P49" s="27"/>
+      <c r="Q49" s="27"/>
+      <c r="R49" s="27"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+      <c r="U49" s="27"/>
+      <c r="V49" s="27"/>
+      <c r="W49" s="27"/>
+      <c r="X49" s="27"/>
+      <c r="Y49" s="27"/>
+      <c r="Z49" s="27"/>
+      <c r="AA49" s="27"/>
+      <c r="AB49" s="27"/>
+      <c r="AC49" s="27"/>
+      <c r="AQ49" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="AR49" s="59"/>
+      <c r="AS49" s="59"/>
+      <c r="AT49" s="59"/>
+      <c r="AU49" s="59"/>
+      <c r="AV49" s="59"/>
+      <c r="AW49" s="59"/>
+      <c r="AX49" s="59"/>
+      <c r="AY49" s="59"/>
+      <c r="AZ49" s="59"/>
+    </row>
+    <row r="50" spans="2:83" ht="15">
+      <c r="D50" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="55"/>
+      <c r="N50" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="28"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+      <c r="AC50" s="28"/>
+      <c r="AQ50" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="AR50" s="27"/>
+      <c r="AS50" s="27"/>
+      <c r="AT50" s="27"/>
+      <c r="AU50" s="27"/>
+      <c r="AV50" s="27"/>
+      <c r="AW50" s="55" t="s">
+        <v>191</v>
+      </c>
+      <c r="AX50" s="55"/>
+      <c r="AY50" s="55"/>
+      <c r="AZ50" s="55"/>
+      <c r="BA50" s="55"/>
+      <c r="BB50" s="55"/>
+      <c r="BC50" s="55"/>
+      <c r="BD50" s="55"/>
+      <c r="BE50" s="55"/>
+      <c r="BF50" s="55"/>
+      <c r="BG50" s="55"/>
+      <c r="BH50" s="55"/>
+      <c r="BI50" s="55"/>
+      <c r="BJ50" s="55"/>
+      <c r="BK50" s="55"/>
+      <c r="BL50" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="BM50" s="27"/>
+      <c r="BN50" s="27"/>
+      <c r="BO50" s="27"/>
+      <c r="BP50" s="27"/>
+      <c r="BQ50" s="27"/>
+      <c r="BR50" s="27"/>
+      <c r="BS50" s="27"/>
+      <c r="BT50" s="27"/>
+      <c r="BU50" s="27"/>
+      <c r="BV50" s="27"/>
+      <c r="BW50" s="27"/>
+      <c r="BX50" s="27"/>
+      <c r="BY50" s="27"/>
+      <c r="BZ50" s="27"/>
+      <c r="CA50" s="27"/>
+      <c r="CB50" s="27"/>
+      <c r="CC50" s="27"/>
+      <c r="CD50" s="27"/>
+      <c r="CE50" s="27"/>
+    </row>
+    <row r="51" spans="2:83" ht="15">
+      <c r="D51" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="55"/>
+      <c r="N51" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="S51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="28"/>
+      <c r="AA51" s="28"/>
+      <c r="AB51" s="28"/>
+      <c r="AC51" s="28"/>
+      <c r="AQ51" s="55" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR51" s="55"/>
+      <c r="AS51" s="55"/>
+      <c r="AT51" s="55"/>
+      <c r="AU51" s="55"/>
+      <c r="AV51" s="55"/>
+      <c r="AW51" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="AX51" s="28"/>
+      <c r="AY51" s="28"/>
+      <c r="AZ51" s="28"/>
+      <c r="BA51" s="28"/>
+      <c r="BB51" s="28"/>
+      <c r="BC51" s="28"/>
+      <c r="BD51" s="28"/>
+      <c r="BE51" s="28"/>
+      <c r="BF51" s="28"/>
+      <c r="BG51" s="28"/>
+      <c r="BH51" s="28"/>
+      <c r="BI51" s="28"/>
+      <c r="BJ51" s="28"/>
+      <c r="BK51" s="28"/>
+      <c r="BL51" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM51" s="28"/>
+      <c r="BN51" s="28"/>
+      <c r="BO51" s="28"/>
+      <c r="BP51" s="28"/>
+      <c r="BQ51" s="28"/>
+      <c r="BR51" s="28"/>
+      <c r="BS51" s="28"/>
+      <c r="BT51" s="28"/>
+      <c r="BU51" s="28"/>
+      <c r="BV51" s="28"/>
+      <c r="BW51" s="28"/>
+      <c r="BX51" s="28"/>
+      <c r="BY51" s="28"/>
+      <c r="BZ51" s="28"/>
+      <c r="CA51" s="28"/>
+      <c r="CB51" s="28"/>
+      <c r="CC51" s="28"/>
+      <c r="CD51" s="28"/>
+      <c r="CE51" s="28"/>
+    </row>
+    <row r="52" spans="2:83" ht="15">
+      <c r="D52" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
+      <c r="AC52" s="28"/>
+      <c r="AQ52" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="AR52" s="55"/>
+      <c r="AS52" s="55"/>
+      <c r="AT52" s="55"/>
+      <c r="AU52" s="55"/>
+      <c r="AV52" s="55"/>
+      <c r="AW52" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="AX52" s="28"/>
+      <c r="AY52" s="28"/>
+      <c r="AZ52" s="28"/>
+      <c r="BA52" s="28"/>
+      <c r="BB52" s="28"/>
+      <c r="BC52" s="28"/>
+      <c r="BD52" s="28"/>
+      <c r="BE52" s="28"/>
+      <c r="BF52" s="28"/>
+      <c r="BG52" s="28"/>
+      <c r="BH52" s="28"/>
+      <c r="BI52" s="28"/>
+      <c r="BJ52" s="28"/>
+      <c r="BK52" s="28"/>
+      <c r="BL52" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="BM52" s="28"/>
+      <c r="BN52" s="28"/>
+      <c r="BO52" s="28"/>
+      <c r="BP52" s="28"/>
+      <c r="BQ52" s="28"/>
+      <c r="BR52" s="28"/>
+      <c r="BS52" s="28"/>
+      <c r="BT52" s="28"/>
+      <c r="BU52" s="28"/>
+      <c r="BV52" s="28"/>
+      <c r="BW52" s="28"/>
+      <c r="BX52" s="28"/>
+      <c r="BY52" s="28"/>
+      <c r="BZ52" s="28"/>
+      <c r="CA52" s="28"/>
+      <c r="CB52" s="28"/>
+      <c r="CC52" s="28"/>
+      <c r="CD52" s="28"/>
+      <c r="CE52" s="28"/>
+    </row>
+    <row r="53" spans="2:83" ht="15">
+      <c r="D53" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="55"/>
+      <c r="N53" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="O53" s="28"/>
+      <c r="P53" s="28"/>
+      <c r="Q53" s="28"/>
+      <c r="R53" s="28"/>
+      <c r="S53" s="28"/>
+      <c r="T53" s="28"/>
+      <c r="U53" s="28"/>
+      <c r="V53" s="28"/>
+      <c r="W53" s="28"/>
+      <c r="X53" s="28"/>
+      <c r="Y53" s="28"/>
+      <c r="Z53" s="28"/>
+      <c r="AA53" s="28"/>
+      <c r="AB53" s="28"/>
+      <c r="AC53" s="28"/>
+      <c r="AQ53" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="AR53" s="60"/>
+      <c r="AS53" s="60"/>
+      <c r="AT53" s="60"/>
+      <c r="AU53" s="60"/>
+      <c r="AV53" s="60"/>
+      <c r="AW53" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX53" s="60"/>
+      <c r="AY53" s="60"/>
+      <c r="AZ53" s="60"/>
+      <c r="BA53" s="60"/>
+      <c r="BB53" s="60"/>
+      <c r="BC53" s="60"/>
+      <c r="BD53" s="60"/>
+      <c r="BE53" s="60"/>
+      <c r="BF53" s="60"/>
+      <c r="BG53" s="60"/>
+      <c r="BH53" s="60"/>
+      <c r="BI53" s="60"/>
+      <c r="BJ53" s="60"/>
+      <c r="BK53" s="60"/>
+      <c r="BL53" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="BM53" s="60"/>
+      <c r="BN53" s="60"/>
+      <c r="BO53" s="60"/>
+      <c r="BP53" s="60"/>
+      <c r="BQ53" s="60"/>
+      <c r="BR53" s="60"/>
+      <c r="BS53" s="60"/>
+      <c r="BT53" s="60"/>
+      <c r="BU53" s="60"/>
+      <c r="BV53" s="60"/>
+      <c r="BW53" s="60"/>
+      <c r="BX53" s="60"/>
+      <c r="BY53" s="60"/>
+      <c r="BZ53" s="60"/>
+      <c r="CA53" s="60"/>
+      <c r="CB53" s="60"/>
+      <c r="CC53" s="60"/>
+      <c r="CD53" s="60"/>
+      <c r="CE53" s="60"/>
+    </row>
+    <row r="54" spans="2:83" ht="15">
+      <c r="D54" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="55"/>
+      <c r="N54" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="28"/>
+      <c r="R54" s="28"/>
+      <c r="S54" s="28"/>
+      <c r="T54" s="28"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="28"/>
+      <c r="W54" s="28"/>
+      <c r="X54" s="28"/>
+      <c r="Y54" s="28"/>
+      <c r="Z54" s="28"/>
+      <c r="AA54" s="28"/>
+      <c r="AB54" s="28"/>
+      <c r="AC54" s="28"/>
+      <c r="AQ54" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="AR54" s="55"/>
+      <c r="AS54" s="55"/>
+      <c r="AT54" s="55"/>
+      <c r="AU54" s="55"/>
+      <c r="AV54" s="55"/>
+      <c r="AW54" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="AX54" s="28"/>
+      <c r="AY54" s="28"/>
+      <c r="AZ54" s="28"/>
+      <c r="BA54" s="28"/>
+      <c r="BB54" s="28"/>
+      <c r="BC54" s="28"/>
+      <c r="BD54" s="28"/>
+      <c r="BE54" s="28"/>
+      <c r="BF54" s="28"/>
+      <c r="BG54" s="28"/>
+      <c r="BH54" s="28"/>
+      <c r="BI54" s="28"/>
+      <c r="BJ54" s="28"/>
+      <c r="BK54" s="28"/>
+      <c r="BL54" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="BM54" s="28"/>
+      <c r="BN54" s="28"/>
+      <c r="BO54" s="28"/>
+      <c r="BP54" s="28"/>
+      <c r="BQ54" s="28"/>
+      <c r="BR54" s="28"/>
+      <c r="BS54" s="28"/>
+      <c r="BT54" s="28"/>
+      <c r="BU54" s="28"/>
+      <c r="BV54" s="28"/>
+      <c r="BW54" s="28"/>
+      <c r="BX54" s="28"/>
+      <c r="BY54" s="28"/>
+      <c r="BZ54" s="28"/>
+      <c r="CA54" s="28"/>
+      <c r="CB54" s="28"/>
+      <c r="CC54" s="28"/>
+      <c r="CD54" s="28"/>
+      <c r="CE54" s="28"/>
+    </row>
+    <row r="55" spans="2:83" ht="15">
+      <c r="AQ55" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="AR55" s="55"/>
+      <c r="AS55" s="55"/>
+      <c r="AT55" s="55"/>
+      <c r="AU55" s="55"/>
+      <c r="AV55" s="55"/>
+      <c r="AW55" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="AX55" s="28"/>
+      <c r="AY55" s="28"/>
+      <c r="AZ55" s="28"/>
+      <c r="BA55" s="28"/>
+      <c r="BB55" s="28"/>
+      <c r="BC55" s="28"/>
+      <c r="BD55" s="28"/>
+      <c r="BE55" s="28"/>
+      <c r="BF55" s="28"/>
+      <c r="BG55" s="28"/>
+      <c r="BH55" s="28"/>
+      <c r="BI55" s="28"/>
+      <c r="BJ55" s="28"/>
+      <c r="BK55" s="28"/>
+      <c r="BL55" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="BM55" s="28"/>
+      <c r="BN55" s="28"/>
+      <c r="BO55" s="28"/>
+      <c r="BP55" s="28"/>
+      <c r="BQ55" s="28"/>
+      <c r="BR55" s="28"/>
+      <c r="BS55" s="28"/>
+      <c r="BT55" s="28"/>
+      <c r="BU55" s="28"/>
+      <c r="BV55" s="28"/>
+      <c r="BW55" s="28"/>
+      <c r="BX55" s="28"/>
+      <c r="BY55" s="28"/>
+      <c r="BZ55" s="28"/>
+      <c r="CA55" s="28"/>
+      <c r="CB55" s="28"/>
+      <c r="CC55" s="28"/>
+      <c r="CD55" s="28"/>
+      <c r="CE55" s="28"/>
+    </row>
+    <row r="56" spans="2:83" ht="15">
+      <c r="AQ56" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="AR56" s="55"/>
+      <c r="AS56" s="55"/>
+      <c r="AT56" s="55"/>
+      <c r="AU56" s="55"/>
+      <c r="AV56" s="55"/>
+      <c r="AW56" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="AX56" s="28"/>
+      <c r="AY56" s="28"/>
+      <c r="AZ56" s="28"/>
+      <c r="BA56" s="28"/>
+      <c r="BB56" s="28"/>
+      <c r="BC56" s="28"/>
+      <c r="BD56" s="28"/>
+      <c r="BE56" s="28"/>
+      <c r="BF56" s="28"/>
+      <c r="BG56" s="28"/>
+      <c r="BH56" s="28"/>
+      <c r="BI56" s="28"/>
+      <c r="BJ56" s="28"/>
+      <c r="BK56" s="28"/>
+      <c r="BL56" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="BM56" s="28"/>
+      <c r="BN56" s="28"/>
+      <c r="BO56" s="28"/>
+      <c r="BP56" s="28"/>
+      <c r="BQ56" s="28"/>
+      <c r="BR56" s="28"/>
+      <c r="BS56" s="28"/>
+      <c r="BT56" s="28"/>
+      <c r="BU56" s="28"/>
+      <c r="BV56" s="28"/>
+      <c r="BW56" s="28"/>
+      <c r="BX56" s="28"/>
+      <c r="BY56" s="28"/>
+      <c r="BZ56" s="28"/>
+      <c r="CA56" s="28"/>
+      <c r="CB56" s="28"/>
+      <c r="CC56" s="28"/>
+      <c r="CD56" s="28"/>
+      <c r="CE56" s="28"/>
+    </row>
+    <row r="57" spans="2:83" ht="15">
+      <c r="AQ57" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="AR57" s="55"/>
+      <c r="AS57" s="55"/>
+      <c r="AT57" s="55"/>
+      <c r="AU57" s="55"/>
+      <c r="AV57" s="55"/>
+      <c r="AW57" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="AX57" s="28"/>
+      <c r="AY57" s="28"/>
+      <c r="AZ57" s="28"/>
+      <c r="BA57" s="28"/>
+      <c r="BB57" s="28"/>
+      <c r="BC57" s="28"/>
+      <c r="BD57" s="28"/>
+      <c r="BE57" s="28"/>
+      <c r="BF57" s="28"/>
+      <c r="BG57" s="28"/>
+      <c r="BH57" s="28"/>
+      <c r="BI57" s="28"/>
+      <c r="BJ57" s="28"/>
+      <c r="BK57" s="28"/>
+      <c r="BL57" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="BM57" s="28"/>
+      <c r="BN57" s="28"/>
+      <c r="BO57" s="28"/>
+      <c r="BP57" s="28"/>
+      <c r="BQ57" s="28"/>
+      <c r="BR57" s="28"/>
+      <c r="BS57" s="28"/>
+      <c r="BT57" s="28"/>
+      <c r="BU57" s="28"/>
+      <c r="BV57" s="28"/>
+      <c r="BW57" s="28"/>
+      <c r="BX57" s="28"/>
+      <c r="BY57" s="28"/>
+      <c r="BZ57" s="28"/>
+      <c r="CA57" s="28"/>
+      <c r="CB57" s="28"/>
+      <c r="CC57" s="28"/>
+      <c r="CD57" s="28"/>
+      <c r="CE57" s="28"/>
+    </row>
+    <row r="59" spans="2:83" ht="23.25">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="2:83">
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61" spans="2:83" ht="15">
+      <c r="B61" s="33"/>
+    </row>
+    <row r="62" spans="2:83">
+      <c r="B62" s="5"/>
+    </row>
+    <row r="63" spans="2:83" ht="15">
+      <c r="B63" s="33"/>
+    </row>
+    <row r="64" spans="2:83">
+      <c r="B64" s="5"/>
+    </row>
+    <row r="65" spans="2:2" ht="15">
+      <c r="B65" s="33"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="5"/>
+    </row>
+    <row r="67" spans="2:2" ht="15">
+      <c r="B67" s="33"/>
+    </row>
+    <row r="71" spans="2:2" ht="23.25">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="73" spans="2:2" ht="15">
+      <c r="B73" s="31"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="5"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="5"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="5"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="5"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="5"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="99">
+    <mergeCell ref="BL57:CE57"/>
+    <mergeCell ref="AW57:BK57"/>
+    <mergeCell ref="BL50:CE50"/>
+    <mergeCell ref="BL51:CE51"/>
+    <mergeCell ref="BL52:CE52"/>
+    <mergeCell ref="BL53:CE53"/>
+    <mergeCell ref="BL54:CE54"/>
+    <mergeCell ref="BL55:CE55"/>
+    <mergeCell ref="BL56:CE56"/>
+    <mergeCell ref="AW50:BK50"/>
+    <mergeCell ref="AW51:BK51"/>
+    <mergeCell ref="AW52:BK52"/>
+    <mergeCell ref="AW53:BK53"/>
+    <mergeCell ref="AW54:BK54"/>
+    <mergeCell ref="AW55:BK55"/>
+    <mergeCell ref="AW56:BK56"/>
+    <mergeCell ref="AQ57:AV57"/>
+    <mergeCell ref="AQ52:AV52"/>
+    <mergeCell ref="AQ53:AV53"/>
+    <mergeCell ref="AQ54:AV54"/>
+    <mergeCell ref="AQ55:AV55"/>
+    <mergeCell ref="AQ56:AV56"/>
+    <mergeCell ref="BB40:BO40"/>
+    <mergeCell ref="BB41:BO41"/>
+    <mergeCell ref="BB42:BO42"/>
+    <mergeCell ref="AQ50:AV50"/>
+    <mergeCell ref="AQ51:AV51"/>
+    <mergeCell ref="BB35:BO35"/>
+    <mergeCell ref="BB36:BO36"/>
+    <mergeCell ref="BB37:BO37"/>
+    <mergeCell ref="BB38:BO38"/>
+    <mergeCell ref="BB39:BO39"/>
+    <mergeCell ref="AU35:BA35"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU37:BA37"/>
+    <mergeCell ref="AU38:BA38"/>
+    <mergeCell ref="AU39:BA39"/>
+    <mergeCell ref="AU40:BA40"/>
+    <mergeCell ref="AU41:BA41"/>
+    <mergeCell ref="AU42:BA42"/>
+    <mergeCell ref="AR40:AT40"/>
+    <mergeCell ref="AR41:AT41"/>
+    <mergeCell ref="AR42:AT42"/>
+    <mergeCell ref="AR35:AT35"/>
+    <mergeCell ref="AR36:AT36"/>
+    <mergeCell ref="AR37:AT37"/>
+    <mergeCell ref="AR38:AT38"/>
+    <mergeCell ref="AR39:AT39"/>
+    <mergeCell ref="N54:AC54"/>
+    <mergeCell ref="N49:AC49"/>
+    <mergeCell ref="N50:AC50"/>
+    <mergeCell ref="N51:AC51"/>
+    <mergeCell ref="N52:AC52"/>
+    <mergeCell ref="N53:AC53"/>
+    <mergeCell ref="D49:M49"/>
+    <mergeCell ref="D50:M50"/>
+    <mergeCell ref="D51:M51"/>
+    <mergeCell ref="D52:M52"/>
+    <mergeCell ref="D53:M53"/>
+    <mergeCell ref="D54:M54"/>
+    <mergeCell ref="M42:S42"/>
+    <mergeCell ref="M43:S43"/>
+    <mergeCell ref="M44:S44"/>
+    <mergeCell ref="M45:S45"/>
+    <mergeCell ref="M46:S46"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="G42:L42"/>
+    <mergeCell ref="G43:L43"/>
+    <mergeCell ref="G44:L44"/>
+    <mergeCell ref="G45:L45"/>
+    <mergeCell ref="G46:L46"/>
+    <mergeCell ref="AS19:AW19"/>
+    <mergeCell ref="AS20:AW20"/>
+    <mergeCell ref="AS21:AW21"/>
+    <mergeCell ref="AS22:AW22"/>
+    <mergeCell ref="AX19:BQ19"/>
+    <mergeCell ref="AX20:BQ20"/>
+    <mergeCell ref="AX21:BQ21"/>
+    <mergeCell ref="AX22:BQ22"/>
+    <mergeCell ref="C2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="N3:V3"/>
+    <mergeCell ref="C4:M4"/>
+    <mergeCell ref="N4:V4"/>
     <mergeCell ref="C8:M8"/>
-    <mergeCell ref="N8:X8"/>
+    <mergeCell ref="N8:V8"/>
     <mergeCell ref="C9:M9"/>
-    <mergeCell ref="N9:X9"/>
+    <mergeCell ref="N9:V9"/>
     <mergeCell ref="C5:M5"/>
-    <mergeCell ref="N5:X5"/>
+    <mergeCell ref="N5:V5"/>
     <mergeCell ref="C6:M6"/>
-    <mergeCell ref="N6:X6"/>
+    <mergeCell ref="N6:V6"/>
     <mergeCell ref="C7:M7"/>
-    <mergeCell ref="N7:X7"/>
-    <mergeCell ref="C2:M2"/>
-    <mergeCell ref="N2:X2"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="N3:X3"/>
-    <mergeCell ref="C4:M4"/>
-    <mergeCell ref="N4:X4"/>
+    <mergeCell ref="N7:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
